--- a/src/data/2026_청장_가을영성수련회_방배정안내.xlsx
+++ b/src/data/2026_청장_가을영성수련회_방배정안내.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="109">
   <si>
     <t>방번호</t>
   </si>
@@ -40,288 +40,288 @@
     <t>박용덕</t>
   </si>
   <si>
+    <t>김혜진</t>
+  </si>
+  <si>
+    <t>없음</t>
+  </si>
+  <si>
+    <t>이도형</t>
+  </si>
+  <si>
+    <t>이경민</t>
+  </si>
+  <si>
+    <t>김지혜</t>
+  </si>
+  <si>
+    <t>정진우</t>
+  </si>
+  <si>
+    <t>이윤경</t>
+  </si>
+  <si>
+    <t>경준구</t>
+  </si>
+  <si>
+    <t>문아름</t>
+  </si>
+  <si>
+    <t>유세나</t>
+  </si>
+  <si>
+    <t>정세호</t>
+  </si>
+  <si>
+    <t>최인혜</t>
+  </si>
+  <si>
+    <t>정은선</t>
+  </si>
+  <si>
+    <t>조형찬</t>
+  </si>
+  <si>
+    <t>조경필</t>
+  </si>
+  <si>
+    <t>차준희</t>
+  </si>
+  <si>
+    <t>이강현</t>
+  </si>
+  <si>
+    <t>최나라</t>
+  </si>
+  <si>
+    <t>김소원</t>
+  </si>
+  <si>
+    <t>한결</t>
+  </si>
+  <si>
+    <t>박윤하</t>
+  </si>
+  <si>
+    <t>김혜영</t>
+  </si>
+  <si>
+    <t>한성희</t>
+  </si>
+  <si>
+    <t>박창선</t>
+  </si>
+  <si>
+    <t>이희선</t>
+  </si>
+  <si>
+    <t>1인실 침대 1개</t>
+  </si>
+  <si>
+    <t>원혜정</t>
+  </si>
+  <si>
+    <t>안민기</t>
+  </si>
+  <si>
+    <t>이종윤</t>
+  </si>
+  <si>
+    <t>박재학</t>
+  </si>
+  <si>
+    <t>조승준</t>
+  </si>
+  <si>
+    <t>침대2개+테이블</t>
+  </si>
+  <si>
+    <t>박재현</t>
+  </si>
+  <si>
+    <t>이유영</t>
+  </si>
+  <si>
+    <t>박종언</t>
+  </si>
+  <si>
+    <t>박정아</t>
+  </si>
+  <si>
+    <t>박태성</t>
+  </si>
+  <si>
+    <t>견혜원</t>
+  </si>
+  <si>
+    <t>박현재</t>
+  </si>
+  <si>
+    <t>권순희</t>
+  </si>
+  <si>
+    <t>금동회</t>
+  </si>
+  <si>
+    <t>임채원</t>
+  </si>
+  <si>
+    <t>홍정화</t>
+  </si>
+  <si>
+    <t>황지현</t>
+  </si>
+  <si>
+    <t>5인 이상 온돌</t>
+  </si>
+  <si>
+    <t>김소연</t>
+  </si>
+  <si>
+    <t>박진범</t>
+  </si>
+  <si>
+    <t>김인의</t>
+  </si>
+  <si>
+    <t>김태일</t>
+  </si>
+  <si>
+    <t>김정수</t>
+  </si>
+  <si>
+    <t>김성현</t>
+  </si>
+  <si>
+    <t>전지현</t>
+  </si>
+  <si>
+    <t>이찬희</t>
+  </si>
+  <si>
+    <t>박금지</t>
+  </si>
+  <si>
+    <t>손영진</t>
+  </si>
+  <si>
+    <t>탁지영</t>
+  </si>
+  <si>
+    <t>김학용</t>
+  </si>
+  <si>
+    <t>최호산나</t>
+  </si>
+  <si>
+    <t>이은경</t>
+  </si>
+  <si>
+    <t>김승곤</t>
+  </si>
+  <si>
+    <t>정수현</t>
+  </si>
+  <si>
+    <t>1인실 침대1개</t>
+  </si>
+  <si>
+    <t>이현지</t>
+  </si>
+  <si>
+    <t>김창훈</t>
+  </si>
+  <si>
+    <t>김성철</t>
+  </si>
+  <si>
+    <t>2인실 침대2개+테이블</t>
+  </si>
+  <si>
+    <t>이원택</t>
+  </si>
+  <si>
+    <t>정진호</t>
+  </si>
+  <si>
+    <t>신동협</t>
+  </si>
+  <si>
+    <t>최순익</t>
+  </si>
+  <si>
+    <t>최성우</t>
+  </si>
+  <si>
+    <t>김현우</t>
+  </si>
+  <si>
+    <t>유가득</t>
+  </si>
+  <si>
+    <t>이은애</t>
+  </si>
+  <si>
+    <t>김고은</t>
+  </si>
+  <si>
+    <t>송예지</t>
+  </si>
+  <si>
+    <t>김민정</t>
+  </si>
+  <si>
+    <t>마민하</t>
+  </si>
+  <si>
+    <t>황진영</t>
+  </si>
+  <si>
+    <t>이봉호</t>
+  </si>
+  <si>
+    <t>김태희</t>
+  </si>
+  <si>
+    <t>권상훈</t>
+  </si>
+  <si>
+    <t>안지혜</t>
+  </si>
+  <si>
+    <t>임지수</t>
+  </si>
+  <si>
+    <t>민다정</t>
+  </si>
+  <si>
+    <t>이진규</t>
+  </si>
+  <si>
+    <t>박병진</t>
+  </si>
+  <si>
+    <t>황상준</t>
+  </si>
+  <si>
+    <t>이수영</t>
+  </si>
+  <si>
+    <t>원치현</t>
+  </si>
+  <si>
+    <t>이은정</t>
+  </si>
+  <si>
     <t>윤하나</t>
   </si>
   <si>
-    <t>없음</t>
-  </si>
-  <si>
-    <t>이도형</t>
-  </si>
-  <si>
-    <t>이경민</t>
-  </si>
-  <si>
-    <t>황상준</t>
-  </si>
-  <si>
-    <t>이수영</t>
-  </si>
-  <si>
-    <t>정진우</t>
-  </si>
-  <si>
-    <t>이윤경</t>
-  </si>
-  <si>
-    <t>경준구</t>
-  </si>
-  <si>
     <t>장예권</t>
   </si>
   <si>
     <t>이윤정</t>
   </si>
   <si>
-    <t>정세호</t>
-  </si>
-  <si>
-    <t>최인혜</t>
-  </si>
-  <si>
-    <t>정은선</t>
-  </si>
-  <si>
-    <t>조형찬</t>
-  </si>
-  <si>
-    <t>조경필</t>
-  </si>
-  <si>
-    <t>차준희</t>
-  </si>
-  <si>
-    <t>이강현</t>
-  </si>
-  <si>
-    <t>최나라</t>
-  </si>
-  <si>
-    <t>김소원</t>
-  </si>
-  <si>
-    <t>한결</t>
-  </si>
-  <si>
-    <t>박윤하</t>
-  </si>
-  <si>
-    <t>김혜영</t>
-  </si>
-  <si>
-    <t>한성희</t>
-  </si>
-  <si>
-    <t>박창선</t>
-  </si>
-  <si>
-    <t>이희선</t>
-  </si>
-  <si>
-    <t>1인실 침대 1개</t>
-  </si>
-  <si>
-    <t>원혜정</t>
-  </si>
-  <si>
-    <t>안민기</t>
-  </si>
-  <si>
-    <t>이종윤</t>
-  </si>
-  <si>
-    <t>박재학</t>
-  </si>
-  <si>
-    <t>조승준</t>
-  </si>
-  <si>
-    <t>침대2개+테이블</t>
-  </si>
-  <si>
-    <t>박재현</t>
-  </si>
-  <si>
-    <t>이유영</t>
-  </si>
-  <si>
-    <t>박종언</t>
-  </si>
-  <si>
-    <t>박정아</t>
-  </si>
-  <si>
-    <t>박태성</t>
-  </si>
-  <si>
-    <t>견혜원</t>
-  </si>
-  <si>
-    <t>박현재</t>
-  </si>
-  <si>
-    <t>권순희</t>
-  </si>
-  <si>
-    <t>금동회</t>
-  </si>
-  <si>
-    <t>임채원</t>
-  </si>
-  <si>
-    <t>홍정화</t>
-  </si>
-  <si>
-    <t>황지현</t>
-  </si>
-  <si>
-    <t>5인 이상 온돌</t>
-  </si>
-  <si>
-    <t>원치현</t>
-  </si>
-  <si>
-    <t>이은정</t>
-  </si>
-  <si>
-    <t>김소연</t>
-  </si>
-  <si>
-    <t>박진범</t>
-  </si>
-  <si>
-    <t>김인의</t>
-  </si>
-  <si>
-    <t>김태일</t>
-  </si>
-  <si>
-    <t>김정수</t>
-  </si>
-  <si>
-    <t>김성현</t>
-  </si>
-  <si>
-    <t>전지현</t>
-  </si>
-  <si>
-    <t>이찬희</t>
-  </si>
-  <si>
-    <t>박금지</t>
-  </si>
-  <si>
-    <t>손영진</t>
-  </si>
-  <si>
-    <t>탁지영</t>
-  </si>
-  <si>
-    <t>김학용</t>
-  </si>
-  <si>
-    <t>최호산나</t>
-  </si>
-  <si>
-    <t>이은경</t>
-  </si>
-  <si>
-    <t>김승곤</t>
-  </si>
-  <si>
-    <t>정수현</t>
-  </si>
-  <si>
-    <t>1인실 침대1개</t>
-  </si>
-  <si>
-    <t>이현지</t>
-  </si>
-  <si>
-    <t>김창훈</t>
-  </si>
-  <si>
-    <t>김성철</t>
-  </si>
-  <si>
-    <t>2인실 침대2개+테이블</t>
-  </si>
-  <si>
-    <t>이원택</t>
-  </si>
-  <si>
-    <t>정진호</t>
-  </si>
-  <si>
-    <t>신동협</t>
-  </si>
-  <si>
-    <t>최순익</t>
-  </si>
-  <si>
-    <t>최성우</t>
-  </si>
-  <si>
-    <t>김현우</t>
-  </si>
-  <si>
-    <t>유가득</t>
-  </si>
-  <si>
-    <t>이은애</t>
-  </si>
-  <si>
-    <t>김고은</t>
-  </si>
-  <si>
-    <t>송예지</t>
-  </si>
-  <si>
-    <t>김민정</t>
-  </si>
-  <si>
-    <t>마민하</t>
-  </si>
-  <si>
-    <t>황진영</t>
-  </si>
-  <si>
-    <t>이봉호</t>
-  </si>
-  <si>
-    <t>김태희</t>
-  </si>
-  <si>
-    <t>권상훈</t>
-  </si>
-  <si>
-    <t>안지혜</t>
-  </si>
-  <si>
-    <t>임지수</t>
-  </si>
-  <si>
-    <t>민다정</t>
-  </si>
-  <si>
-    <t>이진규</t>
-  </si>
-  <si>
-    <t>박병진</t>
-  </si>
-  <si>
-    <t>김지혜</t>
-  </si>
-  <si>
-    <t>김혜진</t>
-  </si>
-  <si>
-    <t>문아름</t>
-  </si>
-  <si>
-    <t>유세나</t>
-  </si>
-  <si>
     <t>문주하</t>
   </si>
   <si>
@@ -332,13 +332,19 @@
   </si>
   <si>
     <t>임지윤</t>
+  </si>
+  <si>
+    <t>장로님 &amp;권사님</t>
+  </si>
+  <si>
+    <t>황지수 목사님</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -355,6 +361,11 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -391,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -406,6 +417,12 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,7 +725,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>6</v>
@@ -719,10 +736,10 @@
         <v>506.0</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>6</v>
@@ -733,7 +750,7 @@
         <v>507.0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
@@ -747,10 +764,10 @@
         <v>508.0</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>6</v>
@@ -761,10 +778,10 @@
         <v>509.0</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>6</v>
@@ -775,10 +792,10 @@
         <v>510.0</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>6</v>
@@ -789,7 +806,7 @@
         <v>511.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>10</v>
@@ -803,10 +820,10 @@
         <v>512.0</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>6</v>
@@ -817,10 +834,10 @@
         <v>513.0</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>6</v>
@@ -831,10 +848,10 @@
         <v>514.0</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>6</v>
@@ -845,7 +862,7 @@
         <v>515.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>10</v>
@@ -859,10 +876,10 @@
         <v>517.0</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>6</v>
@@ -883,13 +900,13 @@
         <v>403.0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -899,7 +916,7 @@
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -907,13 +924,13 @@
         <v>413.0</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -921,13 +938,13 @@
         <v>415.0</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
@@ -935,13 +952,13 @@
         <v>417.0</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
@@ -949,13 +966,13 @@
         <v>405.0</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="25">
@@ -963,13 +980,13 @@
         <v>407.0</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26">
@@ -977,13 +994,13 @@
         <v>409.0</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D26" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -991,13 +1008,13 @@
         <v>411.0</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28">
@@ -1005,13 +1022,13 @@
         <v>414.0</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -1019,13 +1036,13 @@
         <v>416.0</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -1033,13 +1050,13 @@
         <v>401.0</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>53</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31">
@@ -1049,7 +1066,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32">
@@ -1059,7 +1076,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
@@ -1069,7 +1086,7 @@
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -1079,7 +1096,7 @@
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35">
@@ -1089,21 +1106,17 @@
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
         <v>301.0</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
       <c r="D36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37">
@@ -1111,13 +1124,13 @@
         <v>302.0</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -1125,13 +1138,13 @@
         <v>303.0</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
@@ -1139,13 +1152,13 @@
         <v>304.0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
@@ -1153,13 +1166,13 @@
         <v>305.0</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -1167,13 +1180,13 @@
         <v>306.0</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
@@ -1181,13 +1194,13 @@
         <v>307.0</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
@@ -1195,13 +1208,13 @@
         <v>308.0</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44">
@@ -1209,13 +1222,13 @@
         <v>309.0</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45">
@@ -1223,13 +1236,13 @@
         <v>310.0</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
@@ -1239,7 +1252,7 @@
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47">
@@ -1247,13 +1260,13 @@
         <v>202.0</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
@@ -1261,13 +1274,13 @@
         <v>203.0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49">
@@ -1275,13 +1288,13 @@
         <v>204.0</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50">
@@ -1289,13 +1302,13 @@
         <v>205.0</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51">
@@ -1303,13 +1316,13 @@
         <v>206.0</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52">
@@ -1317,13 +1330,13 @@
         <v>207.0</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53">
@@ -1331,13 +1344,13 @@
         <v>208.0</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54">
@@ -1345,13 +1358,13 @@
         <v>209.0</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55">
@@ -1359,13 +1372,13 @@
         <v>210.0</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56">
@@ -1373,13 +1386,13 @@
         <v>212.0</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57">
@@ -1387,13 +1400,13 @@
         <v>213.0</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="58">
@@ -1401,13 +1414,13 @@
         <v>214.0</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59">
@@ -1415,13 +1428,13 @@
         <v>215.0</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60">
@@ -1429,23 +1442,27 @@
         <v>216.0</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2">
         <v>217.0</v>
       </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="4"/>
+      <c r="B61" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="D61" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62">
@@ -1459,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63">
@@ -1473,7 +1490,7 @@
         <v>102</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="64">
@@ -1487,7 +1504,7 @@
         <v>104</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65">
@@ -1501,18 +1518,26 @@
         <v>106</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
+      <c r="A66" s="3">
+        <v>601.0</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
     </row>
     <row r="67">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
+      <c r="A67" s="3">
+        <v>605.0</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
     </row>
